--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92566536381</v>
+        <v>46157.93093362551</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93093362551</v>
+        <v>46157.93169916068</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93169916068</v>
+        <v>46157.93398400144</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93398400144</v>
+        <v>46157.93716133707</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93716133707</v>
+        <v>46158.28214741245</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28214741245</v>
+        <v>46158.29676204539</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29676204539</v>
+        <v>46158.29812849572</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29812849572</v>
+        <v>46158.33385722202</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33385722202</v>
+        <v>46158.36855482502</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36855482502</v>
+        <v>46158.37286224582</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
